--- a/StoreAllSheetData.xlsx
+++ b/StoreAllSheetData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\cc-fullstack\backend\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C0C31A-ECD6-4FF1-A5C4-85F5B6B57498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView xWindow="24" yWindow="744" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -380,9 +384,6 @@
     <t>OBC, SC , ST</t>
   </si>
   <si>
-    <t>PM Street Vendor?s AtmaNirbhar Nidhi (PM SVANidhi)</t>
-  </si>
-  <si>
     <t>PM SVANidhi is a micro-credit scheme launched on 1st June 2020 by the MoHUA to provide handholding support to street vendors. The scheme facilitates a working capital collateral-free loan of ?10,000, with subsequent loans of ?20,000 and ?50,000 with a 7% interest subsidy.</t>
   </si>
   <si>
@@ -755,9 +756,6 @@
     <t>https://www.myscheme.gov.in/schemes/pmsfss</t>
   </si>
   <si>
-    <t>PM ? Surya Ghar: Muft Bijli Yojana</t>
-  </si>
-  <si>
     <t>Ministry Of New and Renewable Energy</t>
   </si>
   <si>
@@ -1065,19 +1063,19 @@
   </si>
   <si>
     <t xml:space="preserve">UnEmployed </t>
+  </si>
+  <si>
+    <t>PM Street Vendors AtmaNirbhar Nidhi (PM SVANidhi)</t>
+  </si>
+  <si>
+    <t>PM  Surya Ghar: Muft Bijli Yojana</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1091,346 +1089,16 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1453,319 +1121,30 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2050,37 +1429,37 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T87"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="50.7777777777778" customWidth="1"/>
+    <col min="1" max="1" width="50.77734375" customWidth="1"/>
     <col min="2" max="2" width="10" style="1"/>
-    <col min="3" max="3" width="16.8888888888889" style="1" customWidth="1"/>
-    <col min="4" max="4" width="255.777777777778" customWidth="1"/>
-    <col min="7" max="7" width="14.2222222222222" customWidth="1"/>
-    <col min="8" max="8" width="30.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="19.2222222222222" customWidth="1"/>
-    <col min="10" max="10" width="25.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="255.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="19.21875" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" customWidth="1"/>
     <col min="11" max="11" width="31" customWidth="1"/>
-    <col min="12" max="12" width="52.8888888888889" customWidth="1"/>
-    <col min="13" max="13" width="16.5555555555556" customWidth="1"/>
-    <col min="14" max="14" width="17.2222222222222" customWidth="1"/>
-    <col min="15" max="15" width="26.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="76.6666666666667" customWidth="1"/>
-    <col min="17" max="17" width="33.6666666666667" customWidth="1"/>
-    <col min="18" max="18" width="21.4444444444444" customWidth="1"/>
-    <col min="19" max="19" width="20.7777777777778" customWidth="1"/>
-    <col min="20" max="20" width="24.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="52.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="17.21875" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" customWidth="1"/>
+    <col min="16" max="16" width="76.6640625" customWidth="1"/>
+    <col min="17" max="17" width="33.6640625" customWidth="1"/>
+    <col min="18" max="18" width="21.44140625" customWidth="1"/>
+    <col min="19" max="19" width="20.77734375" customWidth="1"/>
+    <col min="20" max="20" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -2089,60 +1468,60 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2151,13 +1530,13 @@
       <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G2" t="s">
@@ -2204,7 +1583,7 @@
       </c>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2213,13 +1592,13 @@
       <c r="C3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
@@ -2266,7 +1645,7 @@
       </c>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2275,13 +1654,13 @@
       <c r="C4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G4" t="s">
@@ -2328,7 +1707,7 @@
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2337,13 +1716,13 @@
       <c r="C5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G5" t="s">
@@ -2390,7 +1769,7 @@
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2399,13 +1778,13 @@
       <c r="C6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G6" t="s">
@@ -2452,7 +1831,7 @@
       </c>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2461,13 +1840,13 @@
       <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G7" t="s">
@@ -2514,7 +1893,7 @@
       </c>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2523,13 +1902,13 @@
       <c r="C8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G8" t="s">
@@ -2576,7 +1955,7 @@
       </c>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2585,13 +1964,13 @@
       <c r="C9" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
@@ -2638,7 +2017,7 @@
       </c>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2647,13 +2026,13 @@
       <c r="C10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
@@ -2700,7 +2079,7 @@
       </c>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2709,13 +2088,13 @@
       <c r="C11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G11" t="s">
@@ -2762,7 +2141,7 @@
       </c>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>86</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2771,13 +2150,13 @@
       <c r="C12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G12" t="s">
@@ -2824,7 +2203,7 @@
       </c>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>90</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -2833,13 +2212,13 @@
       <c r="C13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G13" t="s">
@@ -2886,7 +2265,7 @@
       </c>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2895,13 +2274,13 @@
       <c r="C14" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
@@ -2948,7 +2327,7 @@
       </c>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2957,13 +2336,13 @@
       <c r="C15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G15" t="s">
@@ -3010,7 +2389,7 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>102</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -3019,13 +2398,13 @@
       <c r="C16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G16" t="s">
@@ -3072,7 +2451,7 @@
       </c>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -3081,13 +2460,13 @@
       <c r="C17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G17" t="s">
@@ -3134,7 +2513,7 @@
       </c>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -3143,13 +2522,13 @@
       <c r="C18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
@@ -3196,8 +2575,8 @@
       </c>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="2" t="s">
-        <v>116</v>
+      <c r="A19" s="1" t="s">
+        <v>343</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
@@ -3205,13 +2584,13 @@
       <c r="C19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
@@ -3258,22 +2637,22 @@
       </c>
     </row>
     <row r="20" spans="1:20">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G20" t="s">
@@ -3320,8 +2699,8 @@
       </c>
     </row>
     <row r="21" spans="1:20">
-      <c r="A21" s="2" t="s">
-        <v>123</v>
+      <c r="A21" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>20</v>
@@ -3329,13 +2708,13 @@
       <c r="C21" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G21" t="s">
@@ -3382,8 +2761,8 @@
       </c>
     </row>
     <row r="22" spans="1:20">
-      <c r="A22" s="2" t="s">
-        <v>126</v>
+      <c r="A22" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>20</v>
@@ -3391,13 +2770,13 @@
       <c r="C22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G22" t="s">
@@ -3444,8 +2823,8 @@
       </c>
     </row>
     <row r="23" spans="1:20">
-      <c r="A23" s="2" t="s">
-        <v>129</v>
+      <c r="A23" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>20</v>
@@ -3453,13 +2832,13 @@
       <c r="C23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G23" t="s">
@@ -3506,8 +2885,8 @@
       </c>
     </row>
     <row r="24" spans="1:20">
-      <c r="A24" s="2" t="s">
-        <v>132</v>
+      <c r="A24" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>98</v>
@@ -3515,13 +2894,13 @@
       <c r="C24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G24" t="s">
@@ -3540,7 +2919,7 @@
         <v>65</v>
       </c>
       <c r="L24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M24" t="s">
         <v>110</v>
@@ -3568,8 +2947,8 @@
       </c>
     </row>
     <row r="25" spans="1:20">
-      <c r="A25" s="2" t="s">
-        <v>136</v>
+      <c r="A25" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>98</v>
@@ -3577,20 +2956,20 @@
       <c r="C25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G25" t="s">
         <v>24</v>
       </c>
       <c r="H25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s">
         <v>42</v>
@@ -3630,8 +3009,8 @@
       </c>
     </row>
     <row r="26" spans="1:20">
-      <c r="A26" s="2" t="s">
-        <v>140</v>
+      <c r="A26" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>20</v>
@@ -3639,13 +3018,13 @@
       <c r="C26" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G26" t="s">
@@ -3679,7 +3058,7 @@
         <v>33</v>
       </c>
       <c r="Q26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R26" t="s">
         <v>35</v>
@@ -3692,22 +3071,22 @@
       </c>
     </row>
     <row r="27" spans="1:20">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G27" t="s">
@@ -3741,7 +3120,7 @@
         <v>33</v>
       </c>
       <c r="Q27" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R27" t="s">
         <v>35</v>
@@ -3754,8 +3133,8 @@
       </c>
     </row>
     <row r="28" spans="1:20">
-      <c r="A28" s="2" t="s">
-        <v>148</v>
+      <c r="A28" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>20</v>
@@ -3763,13 +3142,13 @@
       <c r="C28" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G28" t="s">
@@ -3803,7 +3182,7 @@
         <v>33</v>
       </c>
       <c r="Q28" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R28" t="s">
         <v>35</v>
@@ -3816,22 +3195,22 @@
       </c>
     </row>
     <row r="29" spans="1:20">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G29" t="s">
@@ -3844,16 +3223,16 @@
         <v>42</v>
       </c>
       <c r="J29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L29" t="s">
         <v>108</v>
       </c>
       <c r="M29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N29" t="s">
         <v>110</v>
@@ -3874,12 +3253,12 @@
         <v>36</v>
       </c>
       <c r="T29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
+      <c r="A30" s="1" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>20</v>
@@ -3887,13 +3266,13 @@
       <c r="C30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G30" t="s">
@@ -3927,7 +3306,7 @@
         <v>33</v>
       </c>
       <c r="Q30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R30" t="s">
         <v>59</v>
@@ -3940,8 +3319,8 @@
       </c>
     </row>
     <row r="31" spans="1:20">
-      <c r="A31" s="2" t="s">
-        <v>161</v>
+      <c r="A31" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>20</v>
@@ -3949,13 +3328,13 @@
       <c r="C31" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G31" t="s">
@@ -3989,7 +3368,7 @@
         <v>33</v>
       </c>
       <c r="Q31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R31" t="s">
         <v>35</v>
@@ -4002,8 +3381,8 @@
       </c>
     </row>
     <row r="32" spans="1:20">
-      <c r="A32" s="2" t="s">
-        <v>164</v>
+      <c r="A32" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>20</v>
@@ -4011,13 +3390,13 @@
       <c r="C32" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G32" t="s">
@@ -4039,7 +3418,7 @@
         <v>108</v>
       </c>
       <c r="M32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N32" t="s">
         <v>31</v>
@@ -4064,8 +3443,8 @@
       </c>
     </row>
     <row r="33" spans="1:20">
-      <c r="A33" s="2" t="s">
-        <v>168</v>
+      <c r="A33" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>98</v>
@@ -4073,13 +3452,13 @@
       <c r="C33" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G33" t="s">
@@ -4098,7 +3477,7 @@
         <v>65</v>
       </c>
       <c r="L33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M33" t="s">
         <v>30</v>
@@ -4126,8 +3505,8 @@
       </c>
     </row>
     <row r="34" spans="1:20">
-      <c r="A34" s="2" t="s">
-        <v>171</v>
+      <c r="A34" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>20</v>
@@ -4135,13 +3514,13 @@
       <c r="C34" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G34" t="s">
@@ -4163,7 +3542,7 @@
         <v>108</v>
       </c>
       <c r="M34" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N34" t="s">
         <v>31</v>
@@ -4188,8 +3567,8 @@
       </c>
     </row>
     <row r="35" spans="1:20">
-      <c r="A35" s="2" t="s">
-        <v>174</v>
+      <c r="A35" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>98</v>
@@ -4197,13 +3576,13 @@
       <c r="C35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G35" t="s">
@@ -4225,7 +3604,7 @@
         <v>108</v>
       </c>
       <c r="M35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N35" t="s">
         <v>110</v>
@@ -4234,7 +3613,7 @@
         <v>32</v>
       </c>
       <c r="P35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q35" t="s">
         <v>34</v>
@@ -4250,8 +3629,8 @@
       </c>
     </row>
     <row r="36" spans="1:20">
-      <c r="A36" s="2" t="s">
-        <v>178</v>
+      <c r="A36" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>98</v>
@@ -4259,13 +3638,13 @@
       <c r="C36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G36" t="s">
@@ -4312,8 +3691,8 @@
       </c>
     </row>
     <row r="37" spans="1:20">
-      <c r="A37" s="2" t="s">
-        <v>129</v>
+      <c r="A37" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>98</v>
@@ -4321,13 +3700,13 @@
       <c r="C37" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G37" t="s">
@@ -4349,7 +3728,7 @@
         <v>108</v>
       </c>
       <c r="M37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N37" t="s">
         <v>110</v>
@@ -4374,8 +3753,8 @@
       </c>
     </row>
     <row r="38" spans="1:20">
-      <c r="A38" s="2" t="s">
-        <v>181</v>
+      <c r="A38" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>98</v>
@@ -4383,13 +3762,13 @@
       <c r="C38" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G38" t="s">
@@ -4408,7 +3787,7 @@
         <v>44</v>
       </c>
       <c r="L38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M38" t="s">
         <v>110</v>
@@ -4436,8 +3815,8 @@
       </c>
     </row>
     <row r="39" spans="1:20">
-      <c r="A39" s="2" t="s">
-        <v>184</v>
+      <c r="A39" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>98</v>
@@ -4445,13 +3824,13 @@
       <c r="C39" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G39" t="s">
@@ -4473,7 +3852,7 @@
         <v>108</v>
       </c>
       <c r="M39" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N39" t="s">
         <v>110</v>
@@ -4498,8 +3877,8 @@
       </c>
     </row>
     <row r="40" spans="1:20">
-      <c r="A40" s="2" t="s">
-        <v>187</v>
+      <c r="A40" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>98</v>
@@ -4507,13 +3886,13 @@
       <c r="C40" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G40" t="s">
@@ -4560,8 +3939,8 @@
       </c>
     </row>
     <row r="41" spans="1:20">
-      <c r="A41" s="2" t="s">
-        <v>190</v>
+      <c r="A41" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>98</v>
@@ -4569,13 +3948,13 @@
       <c r="C41" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G41" t="s">
@@ -4594,7 +3973,7 @@
         <v>65</v>
       </c>
       <c r="L41" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M41" t="s">
         <v>110</v>
@@ -4622,8 +4001,8 @@
       </c>
     </row>
     <row r="42" spans="1:20">
-      <c r="A42" s="2" t="s">
-        <v>193</v>
+      <c r="A42" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>98</v>
@@ -4631,13 +4010,13 @@
       <c r="C42" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G42" t="s">
@@ -4684,22 +4063,22 @@
       </c>
     </row>
     <row r="43" spans="1:20">
-      <c r="A43" s="2" t="s">
-        <v>196</v>
+      <c r="A43" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D43" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G43" t="s">
@@ -4721,7 +4100,7 @@
         <v>108</v>
       </c>
       <c r="M43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N43" t="s">
         <v>110</v>
@@ -4746,22 +4125,22 @@
       </c>
     </row>
     <row r="44" spans="1:20">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G44" t="s">
@@ -4808,8 +4187,8 @@
       </c>
     </row>
     <row r="45" spans="1:20">
-      <c r="A45" s="2" t="s">
-        <v>203</v>
+      <c r="A45" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>20</v>
@@ -4817,13 +4196,13 @@
       <c r="C45" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G45" t="s">
@@ -4870,8 +4249,8 @@
       </c>
     </row>
     <row r="46" spans="1:20">
-      <c r="A46" s="2" t="s">
-        <v>206</v>
+      <c r="A46" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>20</v>
@@ -4879,13 +4258,13 @@
       <c r="C46" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G46" t="s">
@@ -4932,8 +4311,8 @@
       </c>
     </row>
     <row r="47" spans="1:20">
-      <c r="A47" s="2" t="s">
-        <v>209</v>
+      <c r="A47" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>20</v>
@@ -4941,13 +4320,13 @@
       <c r="C47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G47" t="s">
@@ -4994,22 +4373,22 @@
       </c>
     </row>
     <row r="48" spans="1:20">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G48" t="s">
@@ -5040,7 +4419,7 @@
         <v>50</v>
       </c>
       <c r="P48" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q48" t="s">
         <v>34</v>
@@ -5056,22 +4435,22 @@
       </c>
     </row>
     <row r="49" spans="1:20">
-      <c r="A49" s="2" t="s">
-        <v>216</v>
+      <c r="A49" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D49" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G49" t="s">
@@ -5118,22 +4497,22 @@
       </c>
     </row>
     <row r="50" spans="1:20">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C50" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G50" t="s">
@@ -5155,7 +4534,7 @@
         <v>108</v>
       </c>
       <c r="M50" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N50" t="s">
         <v>110</v>
@@ -5180,8 +4559,8 @@
       </c>
     </row>
     <row r="51" spans="1:20">
-      <c r="A51" s="2" t="s">
-        <v>223</v>
+      <c r="A51" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>20</v>
@@ -5189,13 +4568,13 @@
       <c r="C51" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G51" t="s">
@@ -5211,7 +4590,7 @@
         <v>64</v>
       </c>
       <c r="K51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -5242,22 +4621,22 @@
       </c>
     </row>
     <row r="52" spans="1:20">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G52" t="s">
@@ -5304,8 +4683,8 @@
       </c>
     </row>
     <row r="53" spans="1:20">
-      <c r="A53" s="2" t="s">
-        <v>231</v>
+      <c r="A53" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>20</v>
@@ -5313,13 +4692,13 @@
       <c r="C53" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G53" t="s">
@@ -5329,7 +4708,7 @@
         <v>25</v>
       </c>
       <c r="I53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J53" t="s">
         <v>64</v>
@@ -5366,8 +4745,8 @@
       </c>
     </row>
     <row r="54" spans="1:20">
-      <c r="A54" s="2" t="s">
-        <v>235</v>
+      <c r="A54" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>20</v>
@@ -5375,13 +4754,13 @@
       <c r="C54" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G54" t="s">
@@ -5412,7 +4791,7 @@
         <v>50</v>
       </c>
       <c r="P54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q54" t="s">
         <v>34</v>
@@ -5428,8 +4807,8 @@
       </c>
     </row>
     <row r="55" spans="1:20">
-      <c r="A55" s="2" t="s">
-        <v>238</v>
+      <c r="A55" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>20</v>
@@ -5437,13 +4816,13 @@
       <c r="C55" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G55" t="s">
@@ -5490,22 +4869,22 @@
       </c>
     </row>
     <row r="56" spans="1:20">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G56" t="s">
@@ -5552,8 +4931,8 @@
       </c>
     </row>
     <row r="57" spans="1:20">
-      <c r="A57" s="2" t="s">
-        <v>245</v>
+      <c r="A57" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>20</v>
@@ -5561,13 +4940,13 @@
       <c r="C57" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="D57" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G57" t="s">
@@ -5614,8 +4993,8 @@
       </c>
     </row>
     <row r="58" spans="1:20">
-      <c r="A58" s="2" t="s">
-        <v>248</v>
+      <c r="A58" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>20</v>
@@ -5623,13 +5002,13 @@
       <c r="C58" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F58" s="2" t="s">
+      <c r="D58" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G58" t="s">
@@ -5676,22 +5055,22 @@
       </c>
     </row>
     <row r="59" spans="1:20">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G59" t="s">
@@ -5713,7 +5092,7 @@
         <v>108</v>
       </c>
       <c r="M59" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N59" t="s">
         <v>31</v>
@@ -5722,7 +5101,7 @@
         <v>50</v>
       </c>
       <c r="P59" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q59" t="s">
         <v>34</v>
@@ -5738,8 +5117,8 @@
       </c>
     </row>
     <row r="60" spans="1:20">
-      <c r="A60" s="2" t="s">
-        <v>256</v>
+      <c r="A60" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>20</v>
@@ -5747,13 +5126,13 @@
       <c r="C60" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="D60" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G60" t="s">
@@ -5772,7 +5151,7 @@
         <v>44</v>
       </c>
       <c r="L60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M60" t="s">
         <v>110</v>
@@ -5784,7 +5163,7 @@
         <v>50</v>
       </c>
       <c r="P60" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="Q60" t="s">
         <v>34</v>
@@ -5800,8 +5179,8 @@
       </c>
     </row>
     <row r="61" spans="1:20">
-      <c r="A61" s="2" t="s">
-        <v>259</v>
+      <c r="A61" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>20</v>
@@ -5809,13 +5188,13 @@
       <c r="C61" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="D61" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G61" t="s">
@@ -5837,7 +5216,7 @@
         <v>108</v>
       </c>
       <c r="M61" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="N61" t="s">
         <v>31</v>
@@ -5846,7 +5225,7 @@
         <v>32</v>
       </c>
       <c r="P61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q61" t="s">
         <v>34</v>
@@ -5862,8 +5241,8 @@
       </c>
     </row>
     <row r="62" spans="1:20">
-      <c r="A62" s="2" t="s">
-        <v>263</v>
+      <c r="A62" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>20</v>
@@ -5871,13 +5250,13 @@
       <c r="C62" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F62" s="2" t="s">
+      <c r="D62" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F62" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G62" t="s">
@@ -5911,7 +5290,7 @@
         <v>33</v>
       </c>
       <c r="Q62" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R62" t="s">
         <v>35</v>
@@ -5924,22 +5303,22 @@
       </c>
     </row>
     <row r="63" spans="1:20">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G63" t="s">
@@ -5986,8 +5365,8 @@
       </c>
     </row>
     <row r="64" spans="1:20">
-      <c r="A64" s="2" t="s">
-        <v>269</v>
+      <c r="A64" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>20</v>
@@ -5995,13 +5374,13 @@
       <c r="C64" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F64" s="2" t="s">
+      <c r="D64" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F64" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G64" t="s">
@@ -6023,7 +5402,7 @@
         <v>108</v>
       </c>
       <c r="M64" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N64" t="s">
         <v>110</v>
@@ -6048,8 +5427,8 @@
       </c>
     </row>
     <row r="65" spans="1:20">
-      <c r="A65" s="2" t="s">
-        <v>273</v>
+      <c r="A65" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>20</v>
@@ -6057,13 +5436,13 @@
       <c r="C65" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="D65" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="F65" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G65" t="s">
@@ -6110,8 +5489,8 @@
       </c>
     </row>
     <row r="66" spans="1:20">
-      <c r="A66" s="2" t="s">
-        <v>276</v>
+      <c r="A66" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>20</v>
@@ -6119,13 +5498,13 @@
       <c r="C66" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F66" s="2" t="s">
+      <c r="D66" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F66" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G66" t="s">
@@ -6147,7 +5526,7 @@
         <v>108</v>
       </c>
       <c r="M66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N66" t="s">
         <v>110</v>
@@ -6172,8 +5551,8 @@
       </c>
     </row>
     <row r="67" spans="1:20">
-      <c r="A67" s="2" t="s">
-        <v>279</v>
+      <c r="A67" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>20</v>
@@ -6181,13 +5560,13 @@
       <c r="C67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F67" s="2" t="s">
+      <c r="D67" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G67" t="s">
@@ -6221,7 +5600,7 @@
         <v>33</v>
       </c>
       <c r="Q67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R67" t="s">
         <v>35</v>
@@ -6234,22 +5613,22 @@
       </c>
     </row>
     <row r="68" spans="1:20">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G68" t="s">
@@ -6296,8 +5675,8 @@
       </c>
     </row>
     <row r="69" spans="1:20">
-      <c r="A69" s="2" t="s">
-        <v>286</v>
+      <c r="A69" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>20</v>
@@ -6305,13 +5684,13 @@
       <c r="C69" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F69" s="2" t="s">
+      <c r="D69" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G69" t="s">
@@ -6358,22 +5737,22 @@
       </c>
     </row>
     <row r="70" spans="1:20">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F70" s="2" t="s">
+      <c r="F70" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G70" t="s">
@@ -6386,10 +5765,10 @@
         <v>42</v>
       </c>
       <c r="J70" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K70" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L70" t="s">
         <v>29</v>
@@ -6420,8 +5799,8 @@
       </c>
     </row>
     <row r="71" spans="1:20">
-      <c r="A71" s="2" t="s">
-        <v>293</v>
+      <c r="A71" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>20</v>
@@ -6429,13 +5808,13 @@
       <c r="C71" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F71" s="2" t="s">
+      <c r="D71" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F71" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G71" t="s">
@@ -6466,7 +5845,7 @@
         <v>50</v>
       </c>
       <c r="P71" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q71" t="s">
         <v>34</v>
@@ -6482,8 +5861,8 @@
       </c>
     </row>
     <row r="72" spans="1:20">
-      <c r="A72" s="2" t="s">
-        <v>296</v>
+      <c r="A72" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>20</v>
@@ -6491,13 +5870,13 @@
       <c r="C72" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="D72" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G72" t="s">
@@ -6544,8 +5923,8 @@
       </c>
     </row>
     <row r="73" spans="1:20">
-      <c r="A73" s="2" t="s">
-        <v>299</v>
+      <c r="A73" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>20</v>
@@ -6553,29 +5932,29 @@
       <c r="C73" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D73" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F73" s="2" t="s">
+      <c r="D73" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G73" t="s">
         <v>70</v>
       </c>
       <c r="H73" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I73" t="s">
         <v>26</v>
       </c>
       <c r="J73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s">
         <v>108</v>
@@ -6606,8 +5985,8 @@
       </c>
     </row>
     <row r="74" spans="1:20">
-      <c r="A74" s="2" t="s">
-        <v>302</v>
+      <c r="A74" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>20</v>
@@ -6615,13 +5994,13 @@
       <c r="C74" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F74" s="2" t="s">
+      <c r="D74" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F74" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G74" t="s">
@@ -6649,13 +6028,13 @@
         <v>31</v>
       </c>
       <c r="O74" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="P74" t="s">
         <v>33</v>
       </c>
       <c r="Q74" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R74" t="s">
         <v>35</v>
@@ -6668,8 +6047,8 @@
       </c>
     </row>
     <row r="75" spans="1:20">
-      <c r="A75" s="2" t="s">
-        <v>306</v>
+      <c r="A75" s="1" t="s">
+        <v>304</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>20</v>
@@ -6677,13 +6056,13 @@
       <c r="C75" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F75" s="2" t="s">
+      <c r="D75" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F75" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G75" t="s">
@@ -6730,8 +6109,8 @@
       </c>
     </row>
     <row r="76" spans="1:20">
-      <c r="A76" s="2" t="s">
-        <v>309</v>
+      <c r="A76" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>98</v>
@@ -6739,13 +6118,13 @@
       <c r="C76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="D76" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G76" t="s">
@@ -6776,7 +6155,7 @@
         <v>50</v>
       </c>
       <c r="P76" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Q76" t="s">
         <v>34</v>
@@ -6792,8 +6171,8 @@
       </c>
     </row>
     <row r="77" spans="1:20">
-      <c r="A77" s="2" t="s">
-        <v>168</v>
+      <c r="A77" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>98</v>
@@ -6801,13 +6180,13 @@
       <c r="C77" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="F77" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G77" t="s">
@@ -6854,22 +6233,22 @@
       </c>
     </row>
     <row r="78" spans="1:20">
-      <c r="A78" s="2" t="s">
-        <v>313</v>
+      <c r="A78" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>98</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F78" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G78" t="s">
@@ -6888,7 +6267,7 @@
         <v>44</v>
       </c>
       <c r="L78" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M78" t="s">
         <v>110</v>
@@ -6916,8 +6295,8 @@
       </c>
     </row>
     <row r="79" spans="1:20">
-      <c r="A79" s="2" t="s">
-        <v>316</v>
+      <c r="A79" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>98</v>
@@ -6925,13 +6304,13 @@
       <c r="C79" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="D79" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>98</v>
       </c>
       <c r="G79" t="s">
@@ -6953,7 +6332,7 @@
         <v>108</v>
       </c>
       <c r="M79" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N79" t="s">
         <v>110</v>
@@ -6978,22 +6357,22 @@
       </c>
     </row>
     <row r="80" spans="1:20">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="F80" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G80" t="s">
@@ -7012,7 +6391,7 @@
         <v>44</v>
       </c>
       <c r="L80" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M80" t="s">
         <v>110</v>
@@ -7040,22 +6419,22 @@
       </c>
     </row>
     <row r="81" spans="1:20">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C81" s="1" t="s">
+      <c r="E81" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F81" s="2" t="s">
+      <c r="F81" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G81" t="s">
@@ -7077,7 +6456,7 @@
         <v>108</v>
       </c>
       <c r="M81" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N81" t="s">
         <v>110</v>
@@ -7102,8 +6481,8 @@
       </c>
     </row>
     <row r="82" spans="1:20">
-      <c r="A82" s="2" t="s">
-        <v>326</v>
+      <c r="A82" s="1" t="s">
+        <v>324</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>20</v>
@@ -7111,13 +6490,13 @@
       <c r="C82" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="D82" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G82" t="s">
@@ -7148,7 +6527,7 @@
         <v>50</v>
       </c>
       <c r="P82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q82" t="s">
         <v>34</v>
@@ -7164,8 +6543,8 @@
       </c>
     </row>
     <row r="83" spans="1:20">
-      <c r="A83" s="2" t="s">
-        <v>329</v>
+      <c r="A83" s="1" t="s">
+        <v>327</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>20</v>
@@ -7173,13 +6552,13 @@
       <c r="C83" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="D83" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G83" t="s">
@@ -7226,22 +6605,22 @@
       </c>
     </row>
     <row r="84" spans="1:20">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E84" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F84" s="2" t="s">
+      <c r="F84" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G84" t="s">
@@ -7288,8 +6667,8 @@
       </c>
     </row>
     <row r="85" spans="1:20">
-      <c r="A85" s="2" t="s">
-        <v>335</v>
+      <c r="A85" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>20</v>
@@ -7297,13 +6676,13 @@
       <c r="C85" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F85" s="2" t="s">
+      <c r="D85" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G85" t="s">
@@ -7350,8 +6729,8 @@
       </c>
     </row>
     <row r="86" spans="1:20">
-      <c r="A86" s="2" t="s">
-        <v>338</v>
+      <c r="A86" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>20</v>
@@ -7359,13 +6738,13 @@
       <c r="C86" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F86" s="2" t="s">
+      <c r="D86" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G86" t="s">
@@ -7399,7 +6778,7 @@
         <v>33</v>
       </c>
       <c r="Q86" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="R86" t="s">
         <v>35</v>
@@ -7412,22 +6791,22 @@
       </c>
     </row>
     <row r="87" spans="1:20">
-      <c r="A87" s="2" t="s">
-        <v>342</v>
+      <c r="A87" s="1" t="s">
+        <v>340</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F87" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G87" t="s">
@@ -7440,7 +6819,7 @@
         <v>26</v>
       </c>
       <c r="J87" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K87" t="s">
         <v>28</v>
@@ -7458,7 +6837,7 @@
         <v>50</v>
       </c>
       <c r="P87" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q87" t="s">
         <v>34</v>
@@ -7474,10 +6853,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T87" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:T87" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/StoreAllSheetData.xlsx
+++ b/StoreAllSheetData.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windo\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BAFF38-8FE9-4A64-B114-14E5FFF0586C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="384" windowWidth="23016" windowHeight="12216" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1704" uniqueCount="340">
   <si>
     <t>Name</t>
   </si>
@@ -37,6 +31,9 @@
     <t>Link</t>
   </si>
   <si>
+    <t>type.1</t>
+  </si>
+  <si>
     <t>Gender</t>
   </si>
   <si>
@@ -898,25 +895,25 @@
     <t>https://www.myscheme.gov.in/schemes/pdfwc</t>
   </si>
   <si>
-    <t>Male, Female</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Married, Single, Widowed</t>
-  </si>
-  <si>
-    <t>Widowed</t>
-  </si>
-  <si>
-    <t>Married</t>
-  </si>
-  <si>
-    <t>Married, Widowed</t>
-  </si>
-  <si>
-    <t>Single</t>
+    <t>Male, Female, Other</t>
+  </si>
+  <si>
+    <t>Female, Other</t>
+  </si>
+  <si>
+    <t>Married, Single, Widowed, Divorced</t>
+  </si>
+  <si>
+    <t>Widowed, Divorced</t>
+  </si>
+  <si>
+    <t>Married, Divorced</t>
+  </si>
+  <si>
+    <t>Married, Widowed, Divorced</t>
+  </si>
+  <si>
+    <t>Single, Divorced</t>
   </si>
   <si>
     <t>APL, BPL</t>
@@ -928,31 +925,25 @@
     <t>APL</t>
   </si>
   <si>
-    <t>UnEmployed</t>
-  </si>
-  <si>
-    <t>Employed, UnEmployed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employed, UnEmployed </t>
-  </si>
-  <si>
-    <t>Employed</t>
-  </si>
-  <si>
-    <t>Minor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnEmployed </t>
-  </si>
-  <si>
-    <t>Government, Private, Self-Employed</t>
-  </si>
-  <si>
-    <t>Self-Employed</t>
-  </si>
-  <si>
-    <t>Government</t>
+    <t>UnEmployed, Retired</t>
+  </si>
+  <si>
+    <t>Employed, UnEmployed, Retired</t>
+  </si>
+  <si>
+    <t>Employed, Retired</t>
+  </si>
+  <si>
+    <t>Minor, Retired</t>
+  </si>
+  <si>
+    <t>Government, Private, Self-Employed, Daily Wage, Business</t>
+  </si>
+  <si>
+    <t>Self-Employed, Daily Wage, Business</t>
+  </si>
+  <si>
+    <t>Government, Daily Wage, Business</t>
   </si>
   <si>
     <t>Hindu, Muslim, Christian, Jain, Buddhist, Sikh</t>
@@ -985,25 +976,28 @@
     <t>ST</t>
   </si>
   <si>
+    <t>1, 2A, 2B, 3A, 3B</t>
+  </si>
+  <si>
     <t>Educated, Uneducated</t>
   </si>
   <si>
     <t>Educated</t>
   </si>
   <si>
-    <t>Primary, Secondary, Higher Secondary, Graduation, Post Graduation</t>
-  </si>
-  <si>
-    <t>Graduation</t>
-  </si>
-  <si>
-    <t>Graduation, Post Graduation</t>
-  </si>
-  <si>
-    <t>Primary, Secondary, Graduation</t>
-  </si>
-  <si>
-    <t>Primary, Secondary</t>
+    <t>Primary, Secondary, Higher Secondary, Graduation, Post Graduation, Doctorate</t>
+  </si>
+  <si>
+    <t>Graduation, Doctorate</t>
+  </si>
+  <si>
+    <t>Graduation, Post Graduation, Doctorate</t>
+  </si>
+  <si>
+    <t>Primary, Secondary, Graduation, Doctorate</t>
+  </si>
+  <si>
+    <t>Primary, Secondary, Doctorate</t>
   </si>
   <si>
     <t>No, Yes</t>
@@ -1021,10 +1015,10 @@
     <t>Diseased</t>
   </si>
   <si>
-    <t>Rent, Own</t>
-  </si>
-  <si>
-    <t>Rent</t>
+    <t>Rent, Own, Government Quarters, Shared</t>
+  </si>
+  <si>
+    <t>Rent, Government Quarters, Shared</t>
   </si>
   <si>
     <t>0-100</t>
@@ -1040,16 +1034,13 @@
   </si>
   <si>
     <t>1-17, 13-19</t>
-  </si>
-  <si>
-    <t>1, 2A, 2B, 3A, 3B</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1099,21 +1090,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1151,7 +1134,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1185,7 +1168,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1220,10 +1202,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1396,15 +1377,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T87"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="13" max="13" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="56.77734375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1421,90 +1398,90 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N2" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O2" t="s">
         <v>321</v>
@@ -1525,48 +1502,48 @@
         <v>335</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N3" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O3" t="s">
         <v>321</v>
@@ -1587,48 +1564,48 @@
         <v>335</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N4" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O4" t="s">
         <v>322</v>
@@ -1649,48 +1626,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H5" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I5" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N5" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O5" t="s">
         <v>321</v>
@@ -1711,48 +1688,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J6" t="s">
         <v>304</v>
       </c>
       <c r="K6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N6" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O6" t="s">
         <v>321</v>
@@ -1773,48 +1750,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J7" t="s">
         <v>305</v>
       </c>
       <c r="K7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N7" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O7" t="s">
         <v>321</v>
@@ -1835,48 +1812,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N8" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O8" t="s">
         <v>322</v>
@@ -1897,48 +1874,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N9" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O9" t="s">
         <v>321</v>
@@ -1959,48 +1936,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N10" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O10" t="s">
         <v>321</v>
@@ -2021,48 +1998,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N11" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O11" t="s">
         <v>321</v>
@@ -2083,48 +2060,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H12" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J12" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N12" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O12" t="s">
         <v>322</v>
@@ -2145,48 +2122,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D13" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N13" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O13" t="s">
         <v>321</v>
@@ -2207,45 +2184,45 @@
         <v>335</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L14" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N14" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O14" t="s">
         <v>322</v>
@@ -2266,48 +2243,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K15" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L15" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N15" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O15" t="s">
         <v>321</v>
@@ -2328,48 +2305,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H16" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I16" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J16" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L16" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M16" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N16" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O16" t="s">
         <v>321</v>
@@ -2390,45 +2367,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J17" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M17" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O17" t="s">
         <v>321</v>
@@ -2449,48 +2426,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H18" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J18" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M18" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N18" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O18" t="s">
         <v>321</v>
@@ -2511,45 +2488,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N19" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O19" t="s">
         <v>321</v>
@@ -2570,45 +2547,45 @@
         <v>338</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J20" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L20" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M20" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N20" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O20" t="s">
         <v>321</v>
@@ -2629,48 +2606,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F21" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H21" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I21" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J21" t="s">
         <v>305</v>
       </c>
       <c r="K21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N21" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O21" t="s">
         <v>321</v>
@@ -2691,48 +2668,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H22" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I22" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J22" t="s">
         <v>305</v>
       </c>
       <c r="K22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N22" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O22" t="s">
         <v>321</v>
@@ -2753,48 +2730,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H23" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J23" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N23" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O23" t="s">
         <v>321</v>
@@ -2815,42 +2792,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C24" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D24" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F24" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J24" t="s">
         <v>305</v>
       </c>
       <c r="K24" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O24" t="s">
         <v>321</v>
@@ -2871,45 +2848,45 @@
         <v>336</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H25" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I25" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J25" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K25" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L25" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O25" t="s">
         <v>321</v>
@@ -2930,48 +2907,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I26" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J26" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N26" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O26" t="s">
         <v>321</v>
@@ -2992,48 +2969,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G27" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H27" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I27" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J27" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M27" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N27" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O27" t="s">
         <v>321</v>
@@ -3054,48 +3031,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H28" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I28" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J28" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L28" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M28" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N28" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O28" t="s">
         <v>321</v>
@@ -3116,42 +3093,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H29" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I29" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J29" t="s">
         <v>306</v>
       </c>
       <c r="L29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O29" t="s">
         <v>321</v>
@@ -3172,48 +3149,48 @@
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H30" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I30" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J30" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N30" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O30" t="s">
         <v>321</v>
@@ -3234,48 +3211,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I31" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J31" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L31" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N31" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O31" t="s">
         <v>321</v>
@@ -3296,48 +3273,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I32" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J32" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K32" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L32" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M32" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N32" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O32" t="s">
         <v>321</v>
@@ -3358,48 +3335,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I33" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J33" t="s">
         <v>305</v>
       </c>
       <c r="K33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L33" t="s">
+        <v>312</v>
+      </c>
+      <c r="M33" t="s">
         <v>313</v>
       </c>
-      <c r="M33" t="s">
-        <v>314</v>
-      </c>
       <c r="N33" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O33" t="s">
         <v>321</v>
@@ -3420,48 +3397,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J34" t="s">
         <v>305</v>
       </c>
       <c r="K34" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N34" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O34" t="s">
         <v>321</v>
@@ -3482,45 +3459,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H35" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I35" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M35" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O35" t="s">
         <v>321</v>
@@ -3541,48 +3518,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" t="s">
         <v>105</v>
       </c>
-      <c r="D36" t="s">
-        <v>160</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="F36" t="s">
-        <v>104</v>
-      </c>
       <c r="G36" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H36" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I36" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J36" t="s">
         <v>305</v>
       </c>
       <c r="K36" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L36" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N36" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O36" t="s">
         <v>321</v>
@@ -3603,42 +3580,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H37" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L37" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O37" t="s">
         <v>321</v>
@@ -3659,42 +3636,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
+        <v>106</v>
+      </c>
+      <c r="D38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F38" t="s">
         <v>105</v>
       </c>
-      <c r="D38" t="s">
-        <v>161</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="F38" t="s">
-        <v>104</v>
-      </c>
       <c r="G38" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H38" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J38" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K38" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O38" t="s">
         <v>321</v>
@@ -3715,45 +3692,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F39" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G39" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H39" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J39" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L39" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O39" t="s">
         <v>322</v>
@@ -3774,48 +3751,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
+        <v>106</v>
+      </c>
+      <c r="D40" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F40" t="s">
         <v>105</v>
       </c>
-      <c r="D40" t="s">
-        <v>163</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F40" t="s">
-        <v>104</v>
-      </c>
       <c r="G40" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H40" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J40" t="s">
         <v>305</v>
       </c>
       <c r="K40" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L40" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M40" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N40" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O40" t="s">
         <v>321</v>
@@ -3836,42 +3813,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D41" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G41" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H41" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I41" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J41" t="s">
         <v>305</v>
       </c>
       <c r="K41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O41" t="s">
         <v>321</v>
@@ -3892,48 +3869,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F42" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G42" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H42" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I42" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J42" t="s">
         <v>305</v>
       </c>
       <c r="K42" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L42" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M42" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N42" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O42" t="s">
         <v>322</v>
@@ -3954,45 +3931,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G43" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H43" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I43" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J43" t="s">
         <v>305</v>
       </c>
       <c r="K43" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L43" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M43" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O43" t="s">
         <v>322</v>
@@ -4013,48 +3990,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C44" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G44" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I44" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J44" t="s">
         <v>305</v>
       </c>
       <c r="K44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N44" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O44" t="s">
         <v>321</v>
@@ -4075,48 +4052,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H45" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I45" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J45" t="s">
         <v>305</v>
       </c>
       <c r="K45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L45" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M45" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N45" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O45" t="s">
         <v>321</v>
@@ -4137,48 +4114,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D46" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H46" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I46" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J46" t="s">
         <v>305</v>
       </c>
       <c r="K46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L46" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N46" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O46" t="s">
         <v>322</v>
@@ -4199,48 +4176,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D47" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H47" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I47" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J47" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K47" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L47" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M47" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N47" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O47" t="s">
         <v>321</v>
@@ -4261,48 +4238,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G48" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H48" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I48" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J48" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N48" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O48" t="s">
         <v>322</v>
@@ -4323,48 +4300,48 @@
         <v>338</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H49" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I49" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J49" t="s">
         <v>305</v>
       </c>
       <c r="K49" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L49" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N49" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O49" t="s">
         <v>321</v>
@@ -4385,45 +4362,45 @@
         <v>338</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G50" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H50" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I50" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J50" t="s">
         <v>305</v>
       </c>
       <c r="K50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M50" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O50" t="s">
         <v>321</v>
@@ -4444,48 +4421,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C51" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H51" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I51" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J51" t="s">
         <v>305</v>
       </c>
       <c r="K51" t="s">
+        <v>309</v>
+      </c>
+      <c r="L51" t="s">
         <v>310</v>
       </c>
-      <c r="L51" t="s">
-        <v>311</v>
-      </c>
       <c r="M51" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N51" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O51" t="s">
         <v>321</v>
@@ -4506,48 +4483,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H52" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I52" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J52" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L52" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M52" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N52" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O52" t="s">
         <v>321</v>
@@ -4568,48 +4545,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C53" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G53" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H53" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I53" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J53" t="s">
         <v>305</v>
       </c>
       <c r="K53" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L53" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M53" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N53" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O53" t="s">
         <v>322</v>
@@ -4630,48 +4607,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D54" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I54" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J54" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L54" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N54" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s">
         <v>322</v>
@@ -4692,48 +4669,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C55" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G55" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I55" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J55" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K55" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L55" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M55" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N55" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O55" t="s">
         <v>322</v>
@@ -4754,45 +4731,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C56" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D56" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G56" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H56" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J56" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K56" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L56" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O56" t="s">
         <v>322</v>
@@ -4813,48 +4790,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C57" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D57" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G57" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H57" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I57" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J57" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K57" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L57" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M57" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N57" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O57" t="s">
         <v>321</v>
@@ -4875,48 +4852,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H58" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I58" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J58" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K58" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L58" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N58" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O58" t="s">
         <v>321</v>
@@ -4937,48 +4914,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H59" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I59" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J59" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K59" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L59" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M59" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N59" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O59" t="s">
         <v>322</v>
@@ -4999,42 +4976,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D60" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F60" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G60" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H60" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J60" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K60" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L60" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O60" t="s">
         <v>322</v>
@@ -5055,48 +5032,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C61" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F61" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G61" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H61" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I61" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J61" t="s">
         <v>304</v>
       </c>
       <c r="K61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L61" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M61" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N61" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O61" t="s">
         <v>321</v>
@@ -5117,48 +5094,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D62" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F62" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G62" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H62" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I62" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J62" t="s">
         <v>304</v>
       </c>
       <c r="K62" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L62" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M62" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N62" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O62" t="s">
         <v>322</v>
@@ -5179,48 +5156,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F63" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H63" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J63" t="s">
         <v>304</v>
       </c>
       <c r="K63" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L63" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M63" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N63" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O63" t="s">
         <v>321</v>
@@ -5241,45 +5218,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D64" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G64" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I64" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J64" t="s">
         <v>304</v>
       </c>
       <c r="K64" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L64" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M64" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O64" t="s">
         <v>321</v>
@@ -5300,48 +5277,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D65" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G65" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H65" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J65" t="s">
         <v>304</v>
       </c>
       <c r="K65" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L65" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M65" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N65" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O65" t="s">
         <v>321</v>
@@ -5362,45 +5339,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H66" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I66" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J66" t="s">
         <v>305</v>
       </c>
       <c r="K66" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L66" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O66" t="s">
         <v>321</v>
@@ -5421,48 +5398,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D67" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F67" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G67" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H67" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I67" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J67" t="s">
         <v>304</v>
       </c>
       <c r="K67" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L67" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M67" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N67" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O67" t="s">
         <v>321</v>
@@ -5483,45 +5460,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D68" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F68" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H68" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I68" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J68" t="s">
         <v>304</v>
       </c>
       <c r="K68" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L68" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O68" t="s">
         <v>322</v>
@@ -5542,48 +5519,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F69" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G69" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I69" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J69" t="s">
         <v>305</v>
       </c>
       <c r="K69" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L69" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M69" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N69" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O69" t="s">
         <v>321</v>
@@ -5604,45 +5581,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D70" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F70" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G70" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H70" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I70" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J70" t="s">
         <v>306</v>
       </c>
       <c r="L70" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M70" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N70" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O70" t="s">
         <v>321</v>
@@ -5663,48 +5640,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D71" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F71" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I71" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J71" t="s">
         <v>304</v>
       </c>
       <c r="K71" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L71" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M71" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N71" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O71" t="s">
         <v>322</v>
@@ -5725,48 +5702,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C72" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D72" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F72" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G72" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J72" t="s">
         <v>304</v>
       </c>
       <c r="K72" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L72" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M72" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N72" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O72" t="s">
         <v>321</v>
@@ -5787,42 +5764,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G73" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H73" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I73" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J73" t="s">
         <v>306</v>
       </c>
       <c r="L73" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M73" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O73" t="s">
         <v>322</v>
@@ -5843,48 +5820,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C74" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D74" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F74" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G74" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H74" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I74" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J74" t="s">
         <v>304</v>
       </c>
       <c r="K74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L74" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M74" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N74" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O74" t="s">
         <v>322</v>
@@ -5905,48 +5882,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F75" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G75" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H75" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I75" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J75" t="s">
         <v>304</v>
       </c>
       <c r="K75" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L75" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M75" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N75" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O75" t="s">
         <v>321</v>
@@ -5967,48 +5944,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C76" t="s">
+        <v>106</v>
+      </c>
+      <c r="D76" t="s">
+        <v>200</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="F76" t="s">
         <v>105</v>
       </c>
-      <c r="D76" t="s">
-        <v>199</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="F76" t="s">
-        <v>104</v>
-      </c>
       <c r="G76" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H76" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I76" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J76" t="s">
         <v>304</v>
       </c>
       <c r="K76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L76" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M76" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N76" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O76" t="s">
         <v>322</v>
@@ -6029,48 +6006,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G77" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I77" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J77" t="s">
         <v>305</v>
       </c>
       <c r="K77" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M77" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N77" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O77" t="s">
         <v>321</v>
@@ -6091,42 +6068,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B78" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D78" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F78" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G78" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H78" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I78" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J78" t="s">
         <v>304</v>
       </c>
       <c r="K78" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L78" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O78" t="s">
         <v>321</v>
@@ -6147,45 +6124,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B79" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C79" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D79" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F79" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I79" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J79" t="s">
         <v>305</v>
       </c>
       <c r="K79" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M79" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O79" t="s">
         <v>321</v>
@@ -6206,42 +6183,42 @@
         <v>337</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B80" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C80" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D80" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F80" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G80" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H80" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I80" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J80" t="s">
         <v>304</v>
       </c>
       <c r="K80" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L80" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O80" t="s">
         <v>321</v>
@@ -6262,45 +6239,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C81" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F81" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G81" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H81" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I81" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J81" t="s">
         <v>304</v>
       </c>
       <c r="K81" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L81" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M81" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O81" t="s">
         <v>321</v>
@@ -6321,48 +6298,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D82" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F82" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G82" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H82" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I82" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J82" t="s">
         <v>304</v>
       </c>
       <c r="K82" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L82" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M82" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N82" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O82" t="s">
         <v>322</v>
@@ -6383,48 +6360,48 @@
         <v>336</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C83" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D83" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F83" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G83" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H83" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I83" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J83" t="s">
         <v>304</v>
       </c>
       <c r="K83" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L83" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M83" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N83" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O83" t="s">
         <v>322</v>
@@ -6445,48 +6422,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B84" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C84" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D84" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F84" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G84" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H84" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I84" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J84" t="s">
         <v>304</v>
       </c>
       <c r="K84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L84" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M84" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N84" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O84" t="s">
         <v>322</v>
@@ -6507,48 +6484,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C85" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D85" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F85" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G85" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H85" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I85" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J85" t="s">
         <v>305</v>
       </c>
       <c r="K85" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L85" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M85" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N85" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O85" t="s">
         <v>321</v>
@@ -6569,48 +6546,48 @@
         <v>337</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C86" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D86" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F86" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H86" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I86" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J86" t="s">
         <v>304</v>
       </c>
       <c r="K86" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L86" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N86" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O86" t="s">
         <v>322</v>
@@ -6631,45 +6608,45 @@
         <v>337</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B87" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87" t="s">
+        <v>126</v>
+      </c>
+      <c r="D87" t="s">
         <v>103</v>
       </c>
-      <c r="C87" t="s">
-        <v>125</v>
-      </c>
-      <c r="D87" t="s">
-        <v>102</v>
-      </c>
       <c r="E87" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F87" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G87" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H87" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I87" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J87" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="L87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M87" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="N87" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="O87" t="s">
         <v>322</v>
@@ -6692,91 +6669,91 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="E7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="E8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="E9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="E10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="E11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="E12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="E13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="E14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="E15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="E16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="E17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="E18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="E19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="E20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="E21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="E22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="E23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="E24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="E25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="E26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="E27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="E28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="E29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="E30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="E31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="E32" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="E33" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="E34" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="E35" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="E36" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="E37" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="E38" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="E39" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="E40" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="E41" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="E42" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="E43" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="E44" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="E45" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="E46" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="E47" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="E48" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="E49" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="E50" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="E51" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="E52" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="E53" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="E54" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="E55" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
-    <hyperlink ref="E56" r:id="rId55" xr:uid="{00000000-0004-0000-0000-000036000000}"/>
-    <hyperlink ref="E57" r:id="rId56" xr:uid="{00000000-0004-0000-0000-000037000000}"/>
-    <hyperlink ref="E58" r:id="rId57" xr:uid="{00000000-0004-0000-0000-000038000000}"/>
-    <hyperlink ref="E59" r:id="rId58" xr:uid="{00000000-0004-0000-0000-000039000000}"/>
-    <hyperlink ref="E60" r:id="rId59" xr:uid="{00000000-0004-0000-0000-00003A000000}"/>
-    <hyperlink ref="E61" r:id="rId60" xr:uid="{00000000-0004-0000-0000-00003B000000}"/>
-    <hyperlink ref="E62" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
-    <hyperlink ref="E63" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
-    <hyperlink ref="E64" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="E65" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
-    <hyperlink ref="E66" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
-    <hyperlink ref="E67" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
-    <hyperlink ref="E68" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
-    <hyperlink ref="E69" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="E70" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
-    <hyperlink ref="E71" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
-    <hyperlink ref="E72" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="E73" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
-    <hyperlink ref="E74" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
-    <hyperlink ref="E75" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
-    <hyperlink ref="E76" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
-    <hyperlink ref="E77" r:id="rId76" xr:uid="{00000000-0004-0000-0000-00004B000000}"/>
-    <hyperlink ref="E78" r:id="rId77" xr:uid="{00000000-0004-0000-0000-00004C000000}"/>
-    <hyperlink ref="E79" r:id="rId78" xr:uid="{00000000-0004-0000-0000-00004D000000}"/>
-    <hyperlink ref="E80" r:id="rId79" xr:uid="{00000000-0004-0000-0000-00004E000000}"/>
-    <hyperlink ref="E81" r:id="rId80" xr:uid="{00000000-0004-0000-0000-00004F000000}"/>
-    <hyperlink ref="E82" r:id="rId81" xr:uid="{00000000-0004-0000-0000-000050000000}"/>
-    <hyperlink ref="E83" r:id="rId82" xr:uid="{00000000-0004-0000-0000-000051000000}"/>
-    <hyperlink ref="E84" r:id="rId83" xr:uid="{00000000-0004-0000-0000-000052000000}"/>
-    <hyperlink ref="E85" r:id="rId84" xr:uid="{00000000-0004-0000-0000-000053000000}"/>
-    <hyperlink ref="E86" r:id="rId85" xr:uid="{00000000-0004-0000-0000-000054000000}"/>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
+    <hyperlink ref="E32" r:id="rId31"/>
+    <hyperlink ref="E33" r:id="rId32"/>
+    <hyperlink ref="E34" r:id="rId33"/>
+    <hyperlink ref="E35" r:id="rId34"/>
+    <hyperlink ref="E36" r:id="rId35"/>
+    <hyperlink ref="E37" r:id="rId36"/>
+    <hyperlink ref="E38" r:id="rId37"/>
+    <hyperlink ref="E39" r:id="rId38"/>
+    <hyperlink ref="E40" r:id="rId39"/>
+    <hyperlink ref="E41" r:id="rId40"/>
+    <hyperlink ref="E42" r:id="rId41"/>
+    <hyperlink ref="E43" r:id="rId42"/>
+    <hyperlink ref="E44" r:id="rId43"/>
+    <hyperlink ref="E45" r:id="rId44"/>
+    <hyperlink ref="E46" r:id="rId45"/>
+    <hyperlink ref="E47" r:id="rId46"/>
+    <hyperlink ref="E48" r:id="rId47"/>
+    <hyperlink ref="E49" r:id="rId48"/>
+    <hyperlink ref="E50" r:id="rId49"/>
+    <hyperlink ref="E51" r:id="rId50"/>
+    <hyperlink ref="E52" r:id="rId51"/>
+    <hyperlink ref="E53" r:id="rId52"/>
+    <hyperlink ref="E54" r:id="rId53"/>
+    <hyperlink ref="E55" r:id="rId54"/>
+    <hyperlink ref="E56" r:id="rId55"/>
+    <hyperlink ref="E57" r:id="rId56"/>
+    <hyperlink ref="E58" r:id="rId57"/>
+    <hyperlink ref="E59" r:id="rId58"/>
+    <hyperlink ref="E60" r:id="rId59"/>
+    <hyperlink ref="E61" r:id="rId60"/>
+    <hyperlink ref="E62" r:id="rId61"/>
+    <hyperlink ref="E63" r:id="rId62"/>
+    <hyperlink ref="E64" r:id="rId63"/>
+    <hyperlink ref="E65" r:id="rId64"/>
+    <hyperlink ref="E66" r:id="rId65"/>
+    <hyperlink ref="E67" r:id="rId66"/>
+    <hyperlink ref="E68" r:id="rId67"/>
+    <hyperlink ref="E69" r:id="rId68"/>
+    <hyperlink ref="E70" r:id="rId69"/>
+    <hyperlink ref="E71" r:id="rId70"/>
+    <hyperlink ref="E72" r:id="rId71"/>
+    <hyperlink ref="E73" r:id="rId72"/>
+    <hyperlink ref="E74" r:id="rId73"/>
+    <hyperlink ref="E75" r:id="rId74"/>
+    <hyperlink ref="E76" r:id="rId75"/>
+    <hyperlink ref="E77" r:id="rId76"/>
+    <hyperlink ref="E78" r:id="rId77"/>
+    <hyperlink ref="E79" r:id="rId78"/>
+    <hyperlink ref="E80" r:id="rId79"/>
+    <hyperlink ref="E81" r:id="rId80"/>
+    <hyperlink ref="E82" r:id="rId81"/>
+    <hyperlink ref="E83" r:id="rId82"/>
+    <hyperlink ref="E84" r:id="rId83"/>
+    <hyperlink ref="E85" r:id="rId84"/>
+    <hyperlink ref="E86" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
